--- a/data/grant_en.xlsx
+++ b/data/grant_en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Mile_CV\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6E18D4-1234-4AD8-AB76-50958E70EEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1604534-3772-4CD2-AEC2-A9F7B8C8DB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
   <si>
     <t>what</t>
   </si>
@@ -140,6 +140,25 @@
   </si>
   <si>
     <t>Jan. 2016 - Dic. 2019</t>
+  </si>
+  <si>
+    <t>Halifax, Canada</t>
+  </si>
+  <si>
+    <t>Project: A Partnership for the Prevention of Sexual Exploitation of Children in Travel and Tourism in
+Colombia</t>
+  </si>
+  <si>
+    <t>\href{https://sshrc-crsh.canada.ca/en.aspx}{Social Sciences and Humanities Research Council}</t>
+  </si>
+  <si>
+    <t>Dic. 2024 - Dic. 2025</t>
+  </si>
+  <si>
+    <t>CAD\$25.000</t>
+  </si>
+  <si>
+    <t>\href{https://sshrc-crsh.canada.ca/en/funding/opportunities/partnership-engage-grants.aspx}{Partnership Engage Grants}, 2024</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.6640625" bestFit="1" customWidth="1"/>
@@ -1016,21 +1035,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1039,7 +1058,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1048,24 +1067,24 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1073,60 +1092,60 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1135,24 +1154,24 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1161,7 +1180,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1170,15 +1189,15 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
@@ -1186,8 +1205,8 @@
       <c r="D15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>33</v>
+      <c r="E15" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1196,7 +1215,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1205,24 +1224,24 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1240,29 +1259,43 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="E23" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -1313,6 +1346,27 @@
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/grant_en.xlsx
+++ b/data/grant_en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Mile_CV\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1604534-3772-4CD2-AEC2-A9F7B8C8DB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D33957-CE84-4D83-A344-E30AF352E940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>what</t>
   </si>
@@ -159,6 +159,18 @@
   </si>
   <si>
     <t>\href{https://sshrc-crsh.canada.ca/en/funding/opportunities/partnership-engage-grants.aspx}{Partnership Engage Grants}, 2024</t>
+  </si>
+  <si>
+    <t>Feb. 2026 - Present</t>
+  </si>
+  <si>
+    <t>Project: Evolutionary functions of infant‑directed speech: Impact on attention, auditory preferences, and early linguistic and musical development</t>
+  </si>
+  <si>
+    <t>COP\$635.000.000</t>
+  </si>
+  <si>
+    <t>XV \href{https://github.com/JDLeongomez/Proyecto-IDS}{XV Internal Call for Financing Research and Technological Innovation Projects El Bosque University}, 2025</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.6640625" bestFit="1" customWidth="1"/>
@@ -1035,21 +1047,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1067,24 +1079,24 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1093,7 +1105,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1102,24 +1114,24 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1127,60 +1139,60 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="13" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1189,24 +1201,24 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,7 +1227,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1224,15 +1236,15 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>7</v>
@@ -1240,8 +1252,8 @@
       <c r="D18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>33</v>
+      <c r="E18" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1250,7 +1262,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1259,24 +1271,24 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1294,29 +1306,43 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="E26" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -1367,6 +1393,27 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
